--- a/DJF/FTs/UAH_ASW SVT_TestProcedures.xlsx
+++ b/DJF/FTs/UAH_ASW SVT_TestProcedures.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julit\OneDrive\Escritorio\Uni\Tercer año\Segundo cuatri\OBDH\Lab\Hito\Entregable 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julit\OneDrive\Documentos\GitHub\obdh_proy_26_julio_bohigas\DJF\FTs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE571DE8-E4B5-46C3-9104-4C9E45C3CCE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B8DE2D5-4338-4EA2-9ADD-464020BEE12D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Front Cover" sheetId="1" r:id="rId1"/>
@@ -841,7 +841,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1013,6 +1013,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1025,11 +1026,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3518,7 +3514,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="24" customHeight="1">
-      <c r="B10" s="90" t="s">
+      <c r="B10" s="91" t="s">
         <v>40</v>
       </c>
       <c r="D10" s="25" t="s">
@@ -3547,7 +3543,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B13" s="89"/>
+      <c r="B13" s="90"/>
       <c r="C13" s="39"/>
       <c r="D13" s="39" t="s">
         <v>45</v>
@@ -4636,7 +4632,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="24" customHeight="1">
-      <c r="B10" s="90" t="s">
+      <c r="B10" s="91" t="s">
         <v>49</v>
       </c>
       <c r="D10" s="25" t="s">
@@ -4665,7 +4661,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B13" s="89"/>
+      <c r="B13" s="90"/>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
       <c r="E13" s="40"/>
@@ -5750,7 +5746,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B10" s="91" t="s">
+      <c r="B10" s="92" t="s">
         <v>55</v>
       </c>
       <c r="D10" s="25" t="s">
@@ -5761,7 +5757,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B11" s="89"/>
+      <c r="B11" s="90"/>
       <c r="C11" s="54"/>
       <c r="D11" s="54"/>
       <c r="E11" s="55"/>
@@ -8184,7 +8180,7 @@
     </row>
     <row r="13" spans="1:5" ht="12.75" customHeight="1">
       <c r="A13" s="70"/>
-      <c r="B13" s="89"/>
+      <c r="B13" s="90"/>
       <c r="E13" s="73"/>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1">
@@ -8237,7 +8233,7 @@
     </row>
     <row r="18" spans="1:5" ht="16.5" customHeight="1">
       <c r="A18" s="70"/>
-      <c r="B18" s="92" t="s">
+      <c r="B18" s="93" t="s">
         <v>87</v>
       </c>
       <c r="C18" s="75"/>
@@ -8250,7 +8246,7 @@
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1">
       <c r="A19" s="70"/>
-      <c r="B19" s="93"/>
+      <c r="B19" s="94"/>
       <c r="C19" s="70"/>
       <c r="D19" s="25" t="s">
         <v>43</v>
@@ -8261,7 +8257,7 @@
     </row>
     <row r="20" spans="1:5" ht="33.75" customHeight="1">
       <c r="A20" s="70"/>
-      <c r="B20" s="93"/>
+      <c r="B20" s="94"/>
       <c r="C20" s="70"/>
       <c r="D20" s="54" t="s">
         <v>88</v>
@@ -8272,7 +8268,7 @@
     </row>
     <row r="21" spans="1:5" ht="56.25" customHeight="1">
       <c r="A21" s="44"/>
-      <c r="B21" s="94"/>
+      <c r="B21" s="95"/>
       <c r="C21" s="76"/>
       <c r="D21" s="25" t="s">
         <v>45</v>
@@ -9393,7 +9389,7 @@
     </row>
     <row r="13" spans="1:7" ht="12.75" customHeight="1">
       <c r="A13" s="70"/>
-      <c r="B13" s="89"/>
+      <c r="B13" s="90"/>
       <c r="E13" s="73"/>
     </row>
     <row r="14" spans="1:7" ht="15.75" customHeight="1">
@@ -9481,7 +9477,7 @@
     </row>
     <row r="21" spans="1:5" ht="12.75" customHeight="1">
       <c r="A21" s="70"/>
-      <c r="B21" s="89"/>
+      <c r="B21" s="90"/>
       <c r="E21" s="73"/>
     </row>
     <row r="22" spans="1:5" ht="12.75" customHeight="1">
@@ -9566,7 +9562,7 @@
     </row>
     <row r="29" spans="1:5" ht="12.75" customHeight="1">
       <c r="A29" s="70"/>
-      <c r="B29" s="89"/>
+      <c r="B29" s="90"/>
       <c r="E29" s="73"/>
     </row>
     <row r="30" spans="1:5" ht="12.75" customHeight="1">
@@ -9651,7 +9647,7 @@
     </row>
     <row r="37" spans="1:5" ht="12.75" customHeight="1">
       <c r="A37" s="70"/>
-      <c r="B37" s="89"/>
+      <c r="B37" s="90"/>
       <c r="E37" s="73"/>
     </row>
     <row r="38" spans="1:5" ht="12.75" customHeight="1">
@@ -9736,8 +9732,8 @@
     </row>
     <row r="45" spans="1:5" ht="12.75" customHeight="1">
       <c r="A45" s="70"/>
-      <c r="B45" s="89"/>
-      <c r="D45" s="95" t="s">
+      <c r="B45" s="90"/>
+      <c r="D45" s="33" t="s">
         <v>127</v>
       </c>
       <c r="E45" s="86" t="s">
@@ -9826,17 +9822,17 @@
     </row>
     <row r="53" spans="1:5" ht="12.75" customHeight="1">
       <c r="A53" s="70"/>
-      <c r="B53" s="96"/>
+      <c r="B53" s="89"/>
       <c r="D53" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="E53" s="97" t="s">
+      <c r="E53" s="86" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="38.4" customHeight="1">
       <c r="A54" s="70"/>
-      <c r="B54" s="89"/>
+      <c r="B54" s="90"/>
       <c r="D54" s="33" t="s">
         <v>121</v>
       </c>
@@ -10910,7 +10906,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="24" customHeight="1">
-      <c r="B10" s="90" t="s">
+      <c r="B10" s="91" t="s">
         <v>95</v>
       </c>
       <c r="C10" s="77"/>
@@ -10932,7 +10928,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="17.25" customHeight="1">
-      <c r="B12" s="89"/>
+      <c r="B12" s="90"/>
       <c r="C12" s="80"/>
       <c r="D12" s="39" t="s">
         <v>45</v>
@@ -10942,7 +10938,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B13" s="90" t="s">
+      <c r="B13" s="91" t="s">
         <v>96</v>
       </c>
       <c r="C13" s="77"/>
@@ -10955,7 +10951,7 @@
       <c r="E14" s="34"/>
     </row>
     <row r="15" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B15" s="89"/>
+      <c r="B15" s="90"/>
       <c r="C15" s="80"/>
       <c r="D15" s="39"/>
       <c r="E15" s="40"/>
